--- a/pds_admin_WB/Backend/Backend/Data_1.xlsx
+++ b/pds_admin_WB/Backend/Backend/Data_1.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2319" uniqueCount="1132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2319" uniqueCount="1137">
   <si>
     <t>State Name</t>
   </si>
@@ -1909,16 +1909,16 @@
     <t>Allocation_Atta</t>
   </si>
   <si>
-    <t>Abc</t>
-  </si>
-  <si>
-    <t>bcd</t>
-  </si>
-  <si>
-    <t>cde</t>
-  </si>
-  <si>
-    <t>def</t>
+    <t xml:space="preserve"> M/S MANOJIT SAHA</t>
+  </si>
+  <si>
+    <t>ABHIJIT  SARKAR</t>
+  </si>
+  <si>
+    <t>ABUL HOSSAIN</t>
+  </si>
+  <si>
+    <t>ADHIR BASUMATA</t>
   </si>
   <si>
     <t>Smart FPS</t>
@@ -1927,10 +1927,28 @@
     <t>Model FPS</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>26.443843</t>
+  </si>
+  <si>
+    <t>26.535997</t>
+  </si>
+  <si>
+    <t>26.57048</t>
+  </si>
+  <si>
+    <t>26.664284</t>
+  </si>
+  <si>
+    <t>89.85445</t>
+  </si>
+  <si>
+    <t>89.185032</t>
+  </si>
+  <si>
+    <t>89.235358</t>
+  </si>
+  <si>
+    <t>89.417867</t>
   </si>
   <si>
     <t>WH_Type</t>
@@ -3376,37 +3394,34 @@
     <t>Storage_Capacity</t>
   </si>
   <si>
-    <t>Ms Doat Ali Mondal And Sons</t>
-  </si>
-  <si>
-    <t>AJOY NATH YADAV</t>
-  </si>
-  <si>
-    <t>Xgy</t>
+    <t>Ms Radha Distributor</t>
+  </si>
+  <si>
+    <t>MURARI LAL AGARWALA</t>
+  </si>
+  <si>
+    <t>MS SOVA RANI MOULICK SONS</t>
   </si>
   <si>
     <t>WholeSale Depo</t>
   </si>
   <si>
-    <t>Wholesale</t>
-  </si>
-  <si>
-    <t>23.870692</t>
-  </si>
-  <si>
-    <t>22.573481</t>
-  </si>
-  <si>
-    <t>26.323061</t>
-  </si>
-  <si>
-    <t>88.536188</t>
-  </si>
-  <si>
-    <t>88.230922</t>
-  </si>
-  <si>
-    <t>89.473179</t>
+    <t>26.480239</t>
+  </si>
+  <si>
+    <t>26.47149</t>
+  </si>
+  <si>
+    <t>26.516597</t>
+  </si>
+  <si>
+    <t>89.508205</t>
+  </si>
+  <si>
+    <t>89.513631</t>
+  </si>
+  <si>
+    <t>89.533654</t>
   </si>
   <si>
     <t>10000</t>
@@ -8908,7 +8923,7 @@
         <v>636</v>
       </c>
       <c r="G2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -8937,10 +8952,10 @@
         <v>635</v>
       </c>
       <c r="F3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -8969,10 +8984,10 @@
         <v>635</v>
       </c>
       <c r="F4" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -9001,10 +9016,10 @@
         <v>635</v>
       </c>
       <c r="F5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="G5" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -9043,7 +9058,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -9052,30 +9067,30 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="B2" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D2" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="E2" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F2" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="G2" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H2" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -9083,22 +9098,22 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D3" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="E3" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F3" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="G3" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="H3" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -9106,22 +9121,22 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D4" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="E4" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F4" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="G4" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="H4" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -9129,22 +9144,22 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D5" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="E5" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F5" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="G5" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="H5" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -9152,22 +9167,22 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D6" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="E6" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F6" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="G6" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="H6" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -9175,22 +9190,22 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D7" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="E7" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F7" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="G7" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="H7" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -9198,22 +9213,22 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D8" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E8" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F8" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="G8" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="H8" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -9221,22 +9236,22 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D9" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="E9" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F9" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="G9" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="H9" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -9244,22 +9259,22 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D10" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="E10" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F10" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="G10" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="H10" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -9267,22 +9282,22 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D11" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="E11" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F11" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="G11" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="H11" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -9290,22 +9305,22 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D12" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E12" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F12" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="G12" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="H12" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -9313,22 +9328,22 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D13" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="E13" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F13" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="G13" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="H13" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -9336,22 +9351,22 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D14" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="E14" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F14" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="G14" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="H14" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -9359,22 +9374,22 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D15" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="E15" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F15" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="G15" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="H15" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -9382,22 +9397,22 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D16" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="E16" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F16" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="G16" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="H16" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -9405,22 +9420,22 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D17" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="E17" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F17" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="G17" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="H17" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -9428,22 +9443,22 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D18" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="E18" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F18" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="G18" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="H18" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="19" spans="2:8">
@@ -9451,22 +9466,22 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D19" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E19" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F19" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="G19" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="H19" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="20" spans="2:8">
@@ -9474,22 +9489,22 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D20" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="E20" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F20" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="G20" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="H20" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="21" spans="2:8">
@@ -9497,22 +9512,22 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D21" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="E21" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F21" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="G21" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="H21" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -9520,22 +9535,22 @@
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D22" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="E22" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F22" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="G22" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="H22" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -9543,22 +9558,22 @@
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D23" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="E23" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F23" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="G23" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="H23" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -9566,22 +9581,22 @@
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D24" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E24" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F24" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="G24" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="H24" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -9589,22 +9604,22 @@
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D25" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E25" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F25" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="G25" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="H25" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="26" spans="2:8">
@@ -9612,22 +9627,22 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D26" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="E26" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F26" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="G26" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="H26" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="27" spans="2:8">
@@ -9635,22 +9650,22 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D27" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="E27" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F27" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="G27" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="H27" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="28" spans="2:8">
@@ -9658,22 +9673,22 @@
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D28" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="E28" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F28" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="G28" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="H28" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="29" spans="2:8">
@@ -9681,22 +9696,22 @@
         <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D29" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E29" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F29" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="G29" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="H29" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="30" spans="2:8">
@@ -9704,22 +9719,22 @@
         <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D30" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E30" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F30" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="G30" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="H30" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="31" spans="2:8">
@@ -9727,22 +9742,22 @@
         <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D31" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="E31" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F31" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="G31" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="H31" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="32" spans="2:8">
@@ -9750,22 +9765,22 @@
         <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D32" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="E32" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F32" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="G32" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="H32" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="33" spans="2:8">
@@ -9773,22 +9788,22 @@
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D33" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="E33" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F33" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="G33" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="H33" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="34" spans="2:8">
@@ -9796,22 +9811,22 @@
         <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D34" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="E34" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F34" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="G34" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="H34" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="35" spans="2:8">
@@ -9819,22 +9834,22 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D35" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="E35" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F35" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="G35" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="H35" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="36" spans="2:8">
@@ -9842,22 +9857,22 @@
         <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D36" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="E36" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F36" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="G36" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="H36" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="37" spans="2:8">
@@ -9865,22 +9880,22 @@
         <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D37" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="E37" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F37" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="G37" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="H37" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="38" spans="2:8">
@@ -9888,22 +9903,22 @@
         <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D38" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="E38" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F38" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="G38" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="H38" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="39" spans="2:8">
@@ -9911,22 +9926,22 @@
         <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D39" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="E39" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F39" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="G39" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="H39" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="40" spans="2:8">
@@ -9934,22 +9949,22 @@
         <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D40" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="E40" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F40" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="G40" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="H40" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="41" spans="2:8">
@@ -9957,22 +9972,22 @@
         <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D41" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E41" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F41" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="G41" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="H41" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="42" spans="2:8">
@@ -9980,22 +9995,22 @@
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D42" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="E42" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F42" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="G42" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="H42" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="43" spans="2:8">
@@ -10003,22 +10018,22 @@
         <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D43" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="E43" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F43" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="G43" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="H43" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="44" spans="2:8">
@@ -10026,22 +10041,22 @@
         <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D44" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="E44" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F44" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="G44" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="H44" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="45" spans="2:8">
@@ -10049,22 +10064,22 @@
         <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D45" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="E45" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F45" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="G45" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="H45" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="46" spans="2:8">
@@ -10072,22 +10087,22 @@
         <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D46" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E46" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F46" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="G46" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="H46" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="47" spans="2:8">
@@ -10095,22 +10110,22 @@
         <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D47" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="E47" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F47" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="G47" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="H47" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="48" spans="2:8">
@@ -10118,22 +10133,22 @@
         <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D48" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="E48" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F48" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="G48" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="H48" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="49" spans="2:8">
@@ -10141,22 +10156,22 @@
         <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D49" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="E49" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F49" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="G49" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="H49" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="50" spans="2:8">
@@ -10164,22 +10179,22 @@
         <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D50" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="E50" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F50" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="G50" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="H50" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="51" spans="2:8">
@@ -10187,22 +10202,22 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D51" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="E51" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F51" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="G51" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="H51" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="52" spans="2:8">
@@ -10210,22 +10225,22 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D52" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="E52" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F52" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="G52" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="H52" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="53" spans="2:8">
@@ -10233,22 +10248,22 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D53" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="E53" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F53" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="G53" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="H53" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="54" spans="2:8">
@@ -10256,22 +10271,22 @@
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D54" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="E54" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F54" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="G54" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="H54" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="55" spans="2:8">
@@ -10279,22 +10294,22 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D55" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="E55" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F55" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="G55" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="H55" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="56" spans="2:8">
@@ -10302,22 +10317,22 @@
         <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D56" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="E56" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F56" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="G56" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="H56" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="57" spans="2:8">
@@ -10325,22 +10340,22 @@
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D57" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="E57" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F57" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="G57" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="H57" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="58" spans="2:8">
@@ -10348,22 +10363,22 @@
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D58" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="E58" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F58" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="G58" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="H58" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="59" spans="2:8">
@@ -10371,22 +10386,22 @@
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D59" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="E59" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F59" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="G59" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="H59" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="60" spans="2:8">
@@ -10394,22 +10409,22 @@
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D60" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="E60" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F60" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="G60" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="H60" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="61" spans="2:8">
@@ -10417,22 +10432,22 @@
         <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D61" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="E61" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F61" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="G61" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="H61" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="62" spans="2:8">
@@ -10440,22 +10455,22 @@
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D62" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="E62" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F62" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="G62" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="H62" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="63" spans="2:8">
@@ -10463,22 +10478,22 @@
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D63" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="E63" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F63" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="G63" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="H63" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="64" spans="2:8">
@@ -10486,22 +10501,22 @@
         <v>21</v>
       </c>
       <c r="C64" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D64" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="E64" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F64" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="G64" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="H64" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="65" spans="2:8">
@@ -10509,22 +10524,22 @@
         <v>19</v>
       </c>
       <c r="C65" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D65" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="E65" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F65" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="G65" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="H65" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="66" spans="2:8">
@@ -10532,22 +10547,22 @@
         <v>19</v>
       </c>
       <c r="C66" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D66" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="E66" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F66" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="G66" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="H66" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="67" spans="2:8">
@@ -10555,22 +10570,22 @@
         <v>19</v>
       </c>
       <c r="C67" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D67" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="E67" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F67" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="G67" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="H67" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="68" spans="2:8">
@@ -10578,22 +10593,22 @@
         <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D68" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="E68" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F68" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="G68" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="H68" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="69" spans="2:8">
@@ -10601,22 +10616,22 @@
         <v>19</v>
       </c>
       <c r="C69" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D69" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="E69" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F69" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="G69" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="H69" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="70" spans="2:8">
@@ -10624,22 +10639,22 @@
         <v>19</v>
       </c>
       <c r="C70" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D70" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E70" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F70" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="G70" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="H70" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="71" spans="2:8">
@@ -10647,22 +10662,22 @@
         <v>20</v>
       </c>
       <c r="C71" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D71" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="E71" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F71" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="G71" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="H71" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="72" spans="2:8">
@@ -10670,22 +10685,22 @@
         <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D72" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="E72" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F72" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="G72" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="H72" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="73" spans="2:8">
@@ -10693,22 +10708,22 @@
         <v>20</v>
       </c>
       <c r="C73" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D73" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="E73" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F73" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="G73" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="H73" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="74" spans="2:8">
@@ -10716,22 +10731,22 @@
         <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D74" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E74" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F74" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="G74" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="H74" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="75" spans="2:8">
@@ -10739,22 +10754,22 @@
         <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D75" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="E75" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F75" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="G75" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="H75" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="76" spans="2:8">
@@ -10762,22 +10777,22 @@
         <v>20</v>
       </c>
       <c r="C76" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D76" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="E76" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F76" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="G76" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="H76" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="77" spans="2:8">
@@ -10785,22 +10800,22 @@
         <v>20</v>
       </c>
       <c r="C77" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D77" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="E77" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F77" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="G77" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="H77" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="78" spans="2:8">
@@ -10808,22 +10823,22 @@
         <v>22</v>
       </c>
       <c r="C78" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D78" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="E78" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F78" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="G78" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="H78" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="79" spans="2:8">
@@ -10831,22 +10846,22 @@
         <v>22</v>
       </c>
       <c r="C79" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D79" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="E79" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F79" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="G79" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="H79" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="80" spans="2:8">
@@ -10854,22 +10869,22 @@
         <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D80" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="E80" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F80" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="G80" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="H80" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -10877,22 +10892,22 @@
         <v>22</v>
       </c>
       <c r="C81" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D81" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="E81" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F81" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="G81" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="H81" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="82" spans="2:8">
@@ -10900,22 +10915,22 @@
         <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D82" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="E82" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F82" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="G82" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="H82" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="83" spans="2:8">
@@ -10923,22 +10938,22 @@
         <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D83" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="E83" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F83" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="G83" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="H83" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -10946,22 +10961,22 @@
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D84" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="E84" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F84" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="G84" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="H84" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="85" spans="2:8">
@@ -10969,22 +10984,22 @@
         <v>21</v>
       </c>
       <c r="C85" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D85" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="E85" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F85" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="G85" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H85" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="86" spans="2:8">
@@ -10992,22 +11007,22 @@
         <v>21</v>
       </c>
       <c r="C86" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D86" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="E86" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F86" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="G86" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="H86" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="87" spans="2:8">
@@ -11015,22 +11030,22 @@
         <v>21</v>
       </c>
       <c r="C87" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D87" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="E87" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F87" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="G87" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="H87" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -11038,22 +11053,22 @@
         <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D88" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="E88" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F88" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="G88" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="H88" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="89" spans="2:8">
@@ -11061,22 +11076,22 @@
         <v>21</v>
       </c>
       <c r="C89" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D89" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="E89" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F89" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="G89" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="H89" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="90" spans="2:8">
@@ -11084,22 +11099,22 @@
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D90" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="E90" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F90" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="G90" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="H90" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -11107,22 +11122,22 @@
         <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D91" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="E91" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F91" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="G91" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="H91" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="92" spans="2:8">
@@ -11130,22 +11145,22 @@
         <v>26</v>
       </c>
       <c r="C92" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D92" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="E92" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F92" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="G92" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="H92" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="93" spans="2:8">
@@ -11153,22 +11168,22 @@
         <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D93" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="E93" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F93" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="G93" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="H93" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="94" spans="2:8">
@@ -11176,22 +11191,22 @@
         <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D94" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="E94" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F94" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="G94" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="H94" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="95" spans="2:8">
@@ -11199,22 +11214,22 @@
         <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D95" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="E95" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F95" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="G95" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="H95" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="96" spans="2:8">
@@ -11222,22 +11237,22 @@
         <v>27</v>
       </c>
       <c r="C96" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D96" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="E96" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F96" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="G96" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="H96" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="97" spans="2:8">
@@ -11245,22 +11260,22 @@
         <v>27</v>
       </c>
       <c r="C97" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D97" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="E97" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F97" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="G97" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="H97" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="98" spans="2:8">
@@ -11268,22 +11283,22 @@
         <v>27</v>
       </c>
       <c r="C98" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D98" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="E98" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F98" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="G98" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="H98" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="99" spans="2:8">
@@ -11291,22 +11306,22 @@
         <v>27</v>
       </c>
       <c r="C99" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D99" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="E99" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F99" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="G99" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="H99" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -11314,22 +11329,22 @@
         <v>27</v>
       </c>
       <c r="C100" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D100" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="E100" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F100" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="G100" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="H100" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="101" spans="2:8">
@@ -11337,22 +11352,22 @@
         <v>27</v>
       </c>
       <c r="C101" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D101" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="E101" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F101" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="G101" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="H101" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="102" spans="2:8">
@@ -11360,22 +11375,22 @@
         <v>27</v>
       </c>
       <c r="C102" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D102" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="E102" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F102" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="G102" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="H102" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -11383,22 +11398,22 @@
         <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D103" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="E103" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F103" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="G103" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="H103" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="104" spans="2:8">
@@ -11406,22 +11421,22 @@
         <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D104" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="E104" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F104" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="G104" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="H104" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="105" spans="2:8">
@@ -11429,22 +11444,22 @@
         <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D105" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="E105" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F105" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="G105" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="H105" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -11452,22 +11467,22 @@
         <v>28</v>
       </c>
       <c r="C106" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D106" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="E106" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F106" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="G106" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="H106" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="107" spans="2:8">
@@ -11475,22 +11490,22 @@
         <v>16</v>
       </c>
       <c r="C107" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D107" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="E107" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F107" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="G107" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="H107" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="108" spans="2:8">
@@ -11498,22 +11513,22 @@
         <v>23</v>
       </c>
       <c r="C108" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D108" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="E108" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F108" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="G108" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="H108" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="109" spans="2:8">
@@ -11521,22 +11536,22 @@
         <v>23</v>
       </c>
       <c r="C109" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D109" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="E109" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F109" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="G109" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="H109" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="110" spans="2:8">
@@ -11544,22 +11559,22 @@
         <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D110" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="E110" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F110" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="G110" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="H110" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="111" spans="2:8">
@@ -11567,22 +11582,22 @@
         <v>18</v>
       </c>
       <c r="C111" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D111" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="E111" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F111" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="G111" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="H111" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="112" spans="2:8">
@@ -11590,22 +11605,22 @@
         <v>18</v>
       </c>
       <c r="C112" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D112" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="E112" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F112" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="G112" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="H112" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="113" spans="2:8">
@@ -11613,22 +11628,22 @@
         <v>18</v>
       </c>
       <c r="C113" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D113" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="E113" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F113" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="G113" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="H113" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="114" spans="2:8">
@@ -11636,22 +11651,22 @@
         <v>18</v>
       </c>
       <c r="C114" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D114" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="E114" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F114" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="G114" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="H114" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="115" spans="2:8">
@@ -11659,22 +11674,22 @@
         <v>29</v>
       </c>
       <c r="C115" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D115" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E115" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F115" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="G115" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="H115" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="116" spans="2:8">
@@ -11682,22 +11697,22 @@
         <v>29</v>
       </c>
       <c r="C116" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D116" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="E116" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F116" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="G116" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="H116" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="117" spans="2:8">
@@ -11705,22 +11720,22 @@
         <v>29</v>
       </c>
       <c r="C117" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D117" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="E117" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F117" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="G117" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="H117" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="118" spans="2:8">
@@ -11728,22 +11743,22 @@
         <v>29</v>
       </c>
       <c r="C118" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D118" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="E118" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F118" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="G118" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="H118" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="119" spans="2:8">
@@ -11751,22 +11766,22 @@
         <v>29</v>
       </c>
       <c r="C119" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D119" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="E119" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F119" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="G119" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="H119" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="120" spans="2:8">
@@ -11774,22 +11789,22 @@
         <v>29</v>
       </c>
       <c r="C120" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D120" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="E120" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F120" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="G120" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="H120" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
     </row>
   </sheetData>
@@ -11813,7 +11828,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -11825,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -11833,22 +11848,22 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="D2" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="G2" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="H2" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -11856,22 +11871,22 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="D3" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="G3" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="H3" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -11879,22 +11894,22 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="D4" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="E4">
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="G4" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="H4" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
